--- a/tools/llm-as-a-judge/dataset/gold/sample.xlsx
+++ b/tools/llm-as-a-judge/dataset/gold/sample.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kanakaya\git\202x\tools\llm-as-a-judge\dataset\gold\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0613AF24-28AC-4D2C-AB5E-4228BAC4A454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="10240" yWindow="60" windowWidth="23870" windowHeight="16310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,14 +24,92 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>original</t>
+  </si>
+  <si>
+    <t>generated</t>
+  </si>
+  <si>
+    <t>政府は本日、電気料金の負担軽減策として補助金制度を延長すると発表した。対象期間は来年3月までで、一般家庭と中小企業が支援対象となる。</t>
+  </si>
+  <si>
+    <t>政府、電気料金補助を来年3月まで延長</t>
+  </si>
+  <si>
+    <t>国内大手メーカーは新型EVを発表した。1回の充電で700キロメートル以上の走行が可能で、年内発売を予定している。</t>
+  </si>
+  <si>
+    <t>大手メーカー、航続700km超の新型EV発表</t>
+  </si>
+  <si>
+    <t>気象庁は関東地方が梅雨入りしたとみられると発表した。平年より3日遅く、今後1週間は雨の日が続く見込み。</t>
+  </si>
+  <si>
+    <t>関東地方が梅雨入り、平年より3日遅れ</t>
+  </si>
+  <si>
+    <t>総務省が公表した調査によると、国内のインターネット利用率は過去最高を更新した。高齢者層での利用拡大が要因とされる。</t>
+  </si>
+  <si>
+    <t>国内ネット利用率が過去最高、高齢者利用が拡大</t>
+  </si>
+  <si>
+    <t>プロ野球の開幕戦で東京タイタンズが大阪シャークスに勝利した。エース投手が完封し、打線も二桁安打を記録した。</t>
+  </si>
+  <si>
+    <t>東京タイタンズ開幕勝利、エースが完封</t>
+  </si>
+  <si>
+    <t>文部科学省は生成AIの教育利用に関する新たなガイドラインを公表した。学校現場での適切な活用を促進する方針。</t>
+  </si>
+  <si>
+    <t>生成AI活用へ新指針、文科省が公表</t>
+  </si>
+  <si>
+    <t>国内の観光客数が前年同月比で15%増加したことが観光庁の発表で分かった。訪日外国人の回復が寄与した。</t>
+  </si>
+  <si>
+    <t>観光客数15%増、訪日需要の回復続く</t>
+  </si>
+  <si>
+    <t>大手コンビニチェーンは食品ロス削減に向け、賞味期限が近い商品の値引きを全国店舗で本格導入すると発表した。</t>
+  </si>
+  <si>
+    <t>コンビニ大手、食品ロス削減へ値引き拡大</t>
+  </si>
+  <si>
+    <t>研究チームは新素材を開発し、従来比で2倍の耐久性を実現したと発表した。航空機部品への応用が期待されている。</t>
+  </si>
+  <si>
+    <t>新素材開発、耐久性2倍で航空機応用に期待</t>
+  </si>
+  <si>
+    <t>東京都は夏場の節電対策としてポイント還元事業を実施すると発表した。家庭での電力使用抑制を後押しする狙い。</t>
+  </si>
+  <si>
+    <t>東京都、節電促進へポイント還元実施</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -53,7 +137,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +414,104 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="129.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>